--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1302,89 +1302,6 @@
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>JOB-1010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EMP-101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Electrician</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Uppal</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>9 AM - 6 PM</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2 years</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Commercial building electrician requirement.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1862,132 +1779,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WRK-504</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>+919848077001</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>te</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Uppal</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Fresher</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WRK-505</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>+919848077002</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>hi</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Uppal</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Fresher</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WRK-506</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>+919848077003</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Uppal</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Fresher</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1999,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2069,102 +1860,6 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Interested</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>APP-10002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>WRK-504</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>+919848077001</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>JOB-1001</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-28 23:21:42</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Interested</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>APP-10003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>WRK-505</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>+919848077002</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>JOB-1001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-28 23:21:42</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Interested</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>APP-10004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>WRK-506</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>+919848077003</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>JOB-1001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-10-28 23:21:43</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>Interested</t>
         </is>
